--- a/src/test/resources/TestDriver/Hearst_VER/ActivityData/VER_AP.xlsx
+++ b/src/test/resources/TestDriver/Hearst_VER/ActivityData/VER_AP.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b68cc7b829e61597/Desktop/Hearst_Project/FullPopulation/AccountingPolicy_by_BrandPlan/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\fyntrac-data\src\test\resources\TestDriver\Hearst_VER\ActivityData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_BA61370190477C8FE51D50F54E5DCE3A77C57A38" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B32395D5-2DDE-49D1-ADA2-817025B57415}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4E06FBE-F89A-47A2-86E1-63008BB43993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Accounting_Policy" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
@@ -1380,7 +1380,7 @@
         <v>13</v>
       </c>
       <c r="C45" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D45" t="s">
         <v>8</v>
